--- a/data/nzd0601/nzd0601.xlsx
+++ b/data/nzd0601/nzd0601.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E400"/>
+  <dimension ref="A1:E403"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8832,6 +8832,69 @@
       <c r="E400" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:11:37+00:00</t>
+        </is>
+      </c>
+      <c r="B401" t="n">
+        <v>290.01</v>
+      </c>
+      <c r="C401" t="n">
+        <v>206.99</v>
+      </c>
+      <c r="D401" t="n">
+        <v>194.52</v>
+      </c>
+      <c r="E401" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:05:35+00:00</t>
+        </is>
+      </c>
+      <c r="B402" t="n">
+        <v>283.83</v>
+      </c>
+      <c r="C402" t="n">
+        <v>205.64</v>
+      </c>
+      <c r="D402" t="n">
+        <v>193.74</v>
+      </c>
+      <c r="E402" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:05:48+00:00</t>
+        </is>
+      </c>
+      <c r="B403" t="n">
+        <v>273.86</v>
+      </c>
+      <c r="C403" t="n">
+        <v>206.83</v>
+      </c>
+      <c r="D403" t="n">
+        <v>191.66</v>
+      </c>
+      <c r="E403" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -8846,7 +8909,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B636"/>
+  <dimension ref="A1:B640"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15209,6 +15272,46 @@
       </c>
       <c r="B636" t="n">
         <v>-0.9399999999999999</v>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" t="inlineStr">
+        <is>
+          <t>2026-07-04 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B637" t="n">
+        <v>0.83</v>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B638" t="n">
+        <v>-1.3</v>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B639" t="n">
+        <v>-1.11</v>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B640" t="n">
+        <v>-0.31</v>
       </c>
     </row>
   </sheetData>
@@ -15371,28 +15474,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>1.404915237207437</v>
+        <v>1.347792751234769</v>
       </c>
       <c r="J2" t="n">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="K2" t="n">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2243834604941952</v>
+        <v>0.2076790548625893</v>
       </c>
       <c r="M2" t="n">
-        <v>12.78839775889906</v>
+        <v>13.04969471802382</v>
       </c>
       <c r="N2" t="n">
-        <v>306.52595702019</v>
+        <v>313.9203180752841</v>
       </c>
       <c r="O2" t="n">
-        <v>17.50788271094452</v>
+        <v>17.7177966484347</v>
       </c>
       <c r="P2" t="n">
-        <v>280.4435003641328</v>
+        <v>281.1655683378679</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -15443,28 +15546,28 @@
         <v>0.0858</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.612701683584034</v>
+        <v>-0.6416865282357566</v>
       </c>
       <c r="J3" t="n">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="K3" t="n">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="L3" t="n">
-        <v>0.02014763936589159</v>
+        <v>0.02233240379143819</v>
       </c>
       <c r="M3" t="n">
-        <v>19.21010441612573</v>
+        <v>19.14305220804919</v>
       </c>
       <c r="N3" t="n">
-        <v>822.1039364329781</v>
+        <v>818.3676231265758</v>
       </c>
       <c r="O3" t="n">
-        <v>28.67235491606816</v>
+        <v>28.60712539082835</v>
       </c>
       <c r="P3" t="n">
-        <v>241.1930983505746</v>
+        <v>241.5590474082311</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -15515,28 +15618,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.52485677165041</v>
+        <v>-1.554098245792551</v>
       </c>
       <c r="J4" t="n">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="K4" t="n">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="L4" t="n">
-        <v>0.171989604094916</v>
+        <v>0.1790427285789794</v>
       </c>
       <c r="M4" t="n">
-        <v>11.91083312861827</v>
+        <v>11.9201331107891</v>
       </c>
       <c r="N4" t="n">
-        <v>502.9241490290441</v>
+        <v>501.632379419795</v>
       </c>
       <c r="O4" t="n">
-        <v>22.42597041443344</v>
+        <v>22.39715114517458</v>
       </c>
       <c r="P4" t="n">
-        <v>252.8097526134511</v>
+        <v>253.1793509474924</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -15574,7 +15677,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E400"/>
+  <dimension ref="A1:E403"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26373,6 +26476,87 @@
         </is>
       </c>
     </row>
+    <row r="401">
+      <c r="A401" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:11:37+00:00</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>-36.89167009086458,174.98753038989614</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>-36.892219154402206,174.98862856355058</t>
+        </is>
+      </c>
+      <c r="D401" t="inlineStr">
+        <is>
+          <t>-36.89292219801766,174.9888188372324</t>
+        </is>
+      </c>
+      <c r="E401" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:05:35+00:00</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>-36.89165848150713,174.98759819840666</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>-36.89221661824192,174.98864337615382</t>
+        </is>
+      </c>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>-36.89292259216838,174.98882757421734</t>
+        </is>
+      </c>
+      <c r="E402" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:05:48+00:00</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>-36.89163975241485,174.98770759170114</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>-36.892218853820346,174.9886303191184</t>
+        </is>
+      </c>
+      <c r="D403" t="inlineStr">
+        <is>
+          <t>-36.89292364323387,174.98885087284413</t>
+        </is>
+      </c>
+      <c r="E403" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0601/nzd0601.xlsx
+++ b/data/nzd0601/nzd0601.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E403"/>
+  <dimension ref="A1:E405"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8893,6 +8893,48 @@
         <v>191.66</v>
       </c>
       <c r="E403" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-12 22:11:29+00:00</t>
+        </is>
+      </c>
+      <c r="B404" t="n">
+        <v>261.39</v>
+      </c>
+      <c r="C404" t="n">
+        <v>206.87</v>
+      </c>
+      <c r="D404" t="n">
+        <v>190.99</v>
+      </c>
+      <c r="E404" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:11:37+00:00</t>
+        </is>
+      </c>
+      <c r="B405" t="n">
+        <v>255.54</v>
+      </c>
+      <c r="C405" t="n">
+        <v>207.71</v>
+      </c>
+      <c r="D405" t="n">
+        <v>192.03</v>
+      </c>
+      <c r="E405" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -8909,7 +8951,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B640"/>
+  <dimension ref="A1:B644"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15312,6 +15354,46 @@
       </c>
       <c r="B640" t="n">
         <v>-0.31</v>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B641" t="n">
+        <v>0.37</v>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" t="inlineStr">
+        <is>
+          <t>2026-08-12 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B642" t="n">
+        <v>-0.17</v>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B643" t="n">
+        <v>-0.13</v>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" t="inlineStr">
+        <is>
+          <t>2026-08-29 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B644" t="n">
+        <v>0.61</v>
       </c>
     </row>
   </sheetData>
@@ -15474,28 +15556,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>1.347792751234769</v>
+        <v>1.285285741250024</v>
       </c>
       <c r="J2" t="n">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="K2" t="n">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2076790548625893</v>
+        <v>0.1858859949494476</v>
       </c>
       <c r="M2" t="n">
-        <v>13.04969471802382</v>
+        <v>13.37554333684596</v>
       </c>
       <c r="N2" t="n">
-        <v>313.9203180752841</v>
+        <v>329.493414754561</v>
       </c>
       <c r="O2" t="n">
-        <v>17.7177966484347</v>
+        <v>18.15195346938067</v>
       </c>
       <c r="P2" t="n">
-        <v>281.1655683378679</v>
+        <v>281.9580645800755</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -15546,28 +15628,28 @@
         <v>0.0858</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.6416865282357566</v>
+        <v>-0.6595362898944237</v>
       </c>
       <c r="J3" t="n">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="K3" t="n">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="L3" t="n">
-        <v>0.02233240379143819</v>
+        <v>0.02376252191070638</v>
       </c>
       <c r="M3" t="n">
-        <v>19.14305220804919</v>
+        <v>19.09522542592804</v>
       </c>
       <c r="N3" t="n">
-        <v>818.3676231265758</v>
+        <v>815.7019768247661</v>
       </c>
       <c r="O3" t="n">
-        <v>28.60712539082835</v>
+        <v>28.56049678882995</v>
       </c>
       <c r="P3" t="n">
-        <v>241.5590474082311</v>
+        <v>241.7851137428907</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -15618,28 +15700,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.554098245792551</v>
+        <v>-1.57477851056134</v>
       </c>
       <c r="J4" t="n">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="K4" t="n">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1790427285789794</v>
+        <v>0.1839530847622515</v>
       </c>
       <c r="M4" t="n">
-        <v>11.9201331107891</v>
+        <v>11.93094621768963</v>
       </c>
       <c r="N4" t="n">
-        <v>501.632379419795</v>
+        <v>501.0208696335644</v>
       </c>
       <c r="O4" t="n">
-        <v>22.39715114517458</v>
+        <v>22.38349547397735</v>
       </c>
       <c r="P4" t="n">
-        <v>253.1793509474924</v>
+        <v>253.4415376200438</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -15677,7 +15759,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E403"/>
+  <dimension ref="A1:E405"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26557,6 +26639,60 @@
         </is>
       </c>
     </row>
+    <row r="404">
+      <c r="A404" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-12 22:11:29+00:00</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>-36.89161632682066,174.98784441552954</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>-36.89221892896581,174.98862988022645</t>
+        </is>
+      </c>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>-36.89292398179725,174.98885837769032</t>
+        </is>
+      </c>
+      <c r="E404" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:11:37+00:00</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>-36.89160533721416,174.9879086031002</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>-36.892220507020276,174.98862066349508</t>
+        </is>
+      </c>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t>-36.89292345626583,174.9888467283768</t>
+        </is>
+      </c>
+      <c r="E405" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0601/nzd0601.xlsx
+++ b/data/nzd0601/nzd0601.xlsx
@@ -8951,7 +8951,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B644"/>
+  <dimension ref="A1:B645"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15394,6 +15394,16 @@
       </c>
       <c r="B644" t="n">
         <v>0.61</v>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" t="inlineStr">
+        <is>
+          <t>2026-09-05 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B645" t="n">
+        <v>-0.49</v>
       </c>
     </row>
   </sheetData>
